--- a/public/datos/plan_cuadrillas_bid.xlsx
+++ b/public/datos/plan_cuadrillas_bid.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AC$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AD$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AD44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,90 +510,95 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Dirección</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sale de</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Duerme en</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Tramo de llegada (min)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Tramo de salida (min)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Carretera del día (min)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Km del día</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Concepto (tablero del Valle)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Dictamen</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Estado (MEN)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Nivel de afectación (MEN)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Tipo de vía</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Por qué</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Vía de acceso</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Coordenada en revisión</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Latitud</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Longitud</t>
         </is>
@@ -651,80 +656,85 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>VEREDA LA CLORINDA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>56.69</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>63.34</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>120</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>51.2</v>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>EL CARMEN - VIA SIMON BOLIVAR CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>3.54959</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>-76.632525</v>
       </c>
     </row>
@@ -780,80 +790,85 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>BORRERO AYERBE</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>62.64</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>67.12</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>129.8</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>62.1</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 16 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>LA JULIA CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>3.574795</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>-76.64960499999999</v>
       </c>
     </row>
@@ -909,80 +924,85 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO EL CARMEN</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>64.3</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>69.73</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>134</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>63.1</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>EL CARMEN - VIA SIMON BOLIVAR CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>3.5527246</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>-76.6515909</v>
       </c>
     </row>
@@ -1038,75 +1058,80 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>CORREG EL PALMAR</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>62.7</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>65.98999999999999</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>128.7</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 9 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>3.6041469</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>-76.6490644</v>
       </c>
     </row>
@@ -1162,75 +1187,80 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>VEREDA JIGUALES</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>82.3</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>76.19</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>158.5</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>3.595044</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>-76.665947</v>
       </c>
     </row>
@@ -1246,11 +1276,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1286,75 +1316,80 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO EL LIMONAR</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>121.24</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>111.62</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>232.9</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>130</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>3.606151</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>-76.70789000000001</v>
       </c>
     </row>
@@ -1374,7 +1409,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1410,80 +1445,85 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO EL TABOR PUENTE BLANCO</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>90.2</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>69.08</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>159.3</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>101.7</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>4.210564</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>-76.38158300000001</v>
       </c>
     </row>
@@ -1503,7 +1543,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1539,80 +1579,85 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>CORREG SALONICA</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>61.99</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>50.65</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>112.6</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>57</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>en revisión de la mesa</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>4.1258314</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>-76.3722336</v>
       </c>
     </row>
@@ -1632,7 +1677,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1668,80 +1713,85 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>KR 18 15 40</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>46.98</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>0.67</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>48.5</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Carrera 18</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>4.208406</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>-76.31959500000001</v>
       </c>
     </row>
@@ -1761,7 +1811,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1797,70 +1847,75 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>KR 18 15 27</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0.67</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>44.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>48.5</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Carrera 18</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>4.210077</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>-76.319047</v>
       </c>
     </row>
@@ -1880,7 +1935,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1916,80 +1971,85 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>CORREG PORTUGAL DE PIEDRAS</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>41.56</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>40.13</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>81.7</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>58.8</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>4.0553</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>-76.35465000000001</v>
       </c>
     </row>
@@ -2005,11 +2065,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2045,80 +2105,85 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO SANTA MARIA</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>118.92</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>93.52</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>212.4</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>123.5</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 7 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>SANTA MARIA - EL LIMONAR CRUCE VIA 23319VL02 K5+555</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>3.63352</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>-76.715591</v>
       </c>
     </row>
@@ -2174,80 +2239,85 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>KR 3 2 000</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>76.88</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>85.62</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>162.5</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>71.2</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>Carrera 2</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>3.6489149</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>-76.56672399999999</v>
       </c>
     </row>
@@ -2303,80 +2373,85 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>KR 1 3 14</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>76.91</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>95.70999999999999</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>172.6</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>94.8</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 49 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>Diagonal 1</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>3.6478665</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>-76.56629270000001</v>
       </c>
     </row>
@@ -2432,80 +2507,85 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>CL 7 9 11</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>0.23</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>2.2</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>0.6</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>Calle 7</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>3.407489</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>-76.34917799999999</v>
       </c>
     </row>
@@ -2561,80 +2641,85 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>CL 7 8 42</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>0.25</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>2.2</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>0.6</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>Calle 7</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>3.40761667</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>-76.34858894</v>
       </c>
     </row>
@@ -2690,70 +2775,75 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>CR 21 NO 9-89</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>27.65</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>28.95</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>44</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Calle 10</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>3.32644406118</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>-76.23742270629999</v>
       </c>
     </row>
@@ -2809,80 +2899,85 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>CR 12 NO 10-81</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>28.95</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>8.539999999999999</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>44</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>CALLEJON FLORO MERCADO CRUCE VIA 13025VL04-2E</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>3.39537597879</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>-76.3859481842</v>
       </c>
     </row>
@@ -2938,75 +3033,80 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO VILLAMARIA</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>69.45999999999999</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>15.26</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>114.2</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>3.716456</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>-76.47793299999999</v>
       </c>
     </row>
@@ -3062,80 +3162,85 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>KR 4 5 34</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>15.26</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>29.46</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>114.2</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Carrera 4</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>3.699871998710244</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>-76.44279828333418</v>
       </c>
     </row>
@@ -3151,11 +3256,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3191,80 +3296,85 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>KR 6 6 67</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>0.73</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>0.37</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>3.1</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>0.8</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>Carrera 6</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>3.85991597259148</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>-76.38388046730552</v>
       </c>
     </row>
@@ -3280,11 +3390,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3320,80 +3430,85 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
           <t>KR 5 5 79</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>0.37</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>1.99</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>3.1</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>0.8</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>Calle 6</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>3.86056963997</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>-76.38430955440001</v>
       </c>
     </row>
@@ -3413,7 +3528,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3449,80 +3564,85 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>VEREDA SAN JUAN</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>59.23</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>63.8</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>123</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>46.8</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>MEDIACANOA - MIRAVALLE - CAMPO ALEGRE - CRUCE VIA 2302</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>3.962278</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>-76.40526699999999</v>
       </c>
     </row>
@@ -3542,7 +3662,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3578,80 +3698,85 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO  MEDIA CANOA</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>9.4</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>40.8</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>62.9</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 24 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>MEDIACANOA - PRIMAVERA</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>3.900556391368746</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>-76.37662112784321</v>
       </c>
     </row>
@@ -3671,7 +3796,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3707,80 +3832,85 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>KR 9 13 08</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>40.8</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>43.4</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>62.9</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 31 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>Carrera 9</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>3.82299113556</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>-76.52146344489999</v>
       </c>
     </row>
@@ -3800,7 +3930,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3836,80 +3966,85 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
           <t>VEREDA CAIMITAL</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>59.58</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>63.82</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>123.4</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>81.2</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 32 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>EL TAMBOR - LA RIVERA - OCACHE</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>3.741864</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
         <v>-76.49940700000001</v>
       </c>
     </row>
@@ -3929,7 +4064,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3965,80 +4100,85 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>CORREG LA MARIA</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>140.39</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>102.33</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>242.7</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>126.3</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>LA GUAIRA - KM113- LOMITAS</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>3.6919524</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
         <v>-76.63414659999999</v>
       </c>
     </row>
@@ -4094,80 +4234,85 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>CORREG EL VILLAR</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Pereira</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>138.32</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>97.67</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>236</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>113.2</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>Colapso total</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 34 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>LA PLAYA CRUCE CON VIA 04123VL13-5G3 EN K3</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>4.819842722212309</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>-76.08934449628445</v>
       </c>
     </row>
@@ -4223,80 +4368,85 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>CORREG EL VERGEL</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>65.8</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>65.38</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>131.2</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>54.1</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>EL VERGEL CRUCE CON VIA 04123VL13-5C EN K6+384</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
         <v>4.86111676163</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
         <v>-75.99733304110001</v>
       </c>
     </row>
@@ -4352,80 +4502,85 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>VEREDA EL PLACER</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>104.08</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>102.25</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>206.3</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>85.8</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>EL REAL PLACER CRUCE CON VIA 0414802VL-G EN K22+316</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>4.7883859</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
         <v>-76.0724936</v>
       </c>
     </row>
@@ -4481,80 +4636,85 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
           <t>VEREDA LA ESTRELLA</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>75.41</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>150.8</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>76.5</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>LAS BRISAS - EL BRILLANTE</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
         <v>4.72634</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
         <v>-76.11562499999999</v>
       </c>
     </row>
@@ -4610,80 +4770,85 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>CORRG SAN FRANCISCO</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>40.95</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>15.49</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>103.2</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>SAN FRANCISCO CRUCE 82323VL02-N K0+000</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
         <v>4.68415925</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AD33" t="n">
         <v>-76.0351458</v>
       </c>
     </row>
@@ -4739,80 +4904,85 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>CLL 18 NO 1-100</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>15.49</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>46.69</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>103.2</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 41 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Calle 18</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
         <v>4.60769678</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AD34" t="n">
         <v>-76.07215911999999</v>
       </c>
     </row>
@@ -4828,11 +4998,11 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4868,65 +5038,70 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
           <t>CORREGIMENTO LA FLORIDA</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>33.24</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>34.3</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>67.5</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>36.4</v>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB35" t="n">
+      <c r="AC35" t="n">
         <v>4.64998614</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AD35" t="n">
         <v>-76.13698533</v>
       </c>
     </row>
@@ -4946,7 +5121,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4982,80 +5157,85 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
           <t>CRA 14 NO 13-25</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>36.24</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>0.17</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>44.3</v>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>Calle 13</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB36" t="n">
+      <c r="AC36" t="n">
         <v>4.5307229</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AD36" t="n">
         <v>-76.1031742</v>
       </c>
     </row>
@@ -5075,7 +5255,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -5111,80 +5291,85 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
           <t>CL 13 14 51</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>0.17</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>39.7</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>44.3</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>Calle 13</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB37" t="n">
+      <c r="AC37" t="n">
         <v>4.5306222</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AD37" t="n">
         <v>-76.10365280000001</v>
       </c>
     </row>
@@ -5204,7 +5389,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -5240,80 +5425,85 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
           <t>CL 16 16 00</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>35.88</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>13.08</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>92.3</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>77.8</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Colapso total</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>Calle 16</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB38" t="n">
+      <c r="AC38" t="n">
         <v>4.53325</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AD38" t="n">
         <v>-76.1032</v>
       </c>
     </row>
@@ -5333,7 +5523,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -5369,80 +5559,85 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
           <t>CL 8 7 61</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>13.08</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>43.36</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>92.3</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>77.8</v>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>Carrera 8</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
         <v>4.522653896403604</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AD39" t="n">
         <v>-76.0369985666723</v>
       </c>
     </row>
@@ -5462,7 +5657,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5498,80 +5693,85 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
           <t>CL 4 5 38</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>48.65</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>14.74</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>114.8</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>98</v>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>Carrera 5</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB40" t="n">
+      <c r="AC40" t="n">
         <v>4.412260842287796</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AD40" t="n">
         <v>-76.15737540436542</v>
       </c>
     </row>
@@ -5591,7 +5791,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5627,80 +5827,85 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
           <t>KR 2 2 66</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>14.74</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>51.29</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>114.8</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>98</v>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 43 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>BOLIVAR CRUCE CON VIA DE INVIAS 2302 EN TRAMO 23020 INICIO A 52m DE INICIO DE VIA 10023VL02B</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB41" t="n">
+      <c r="AC41" t="n">
         <v>4.340805</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AD41" t="n">
         <v>-76.17979800000001</v>
       </c>
     </row>
@@ -5720,7 +5925,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5756,80 +5961,85 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t>CL 6 4 15</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Caicedonia</t>
         </is>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>3.3</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>32.49</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>Calle 6</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB42" t="n">
+      <c r="AC42" t="n">
         <v>4.165067</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AD42" t="n">
         <v>-76.16943499999999</v>
       </c>
     </row>
@@ -5849,7 +6059,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5885,80 +6095,85 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
           <t>CL 10 KR 10 EQ</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Caicedonia</t>
         </is>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>32.49</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>58.56</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>Carrera 10</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB43" t="n">
+      <c r="AC43" t="n">
         <v>4.3959229</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AD43" t="n">
         <v>-76.0708454</v>
       </c>
     </row>
@@ -5974,11 +6189,11 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -6014,85 +6229,90 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
           <t>CL 5 11 15</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Caicedonia</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Pereira</t>
         </is>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>1.47</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>112.59</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>114.1</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>Calle 5</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB44" t="n">
+      <c r="AC44" t="n">
         <v>4.329633623</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AD44" t="n">
         <v>-75.82531724</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC44"/>
+  <autoFilter ref="A1:AD44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6103,7 +6323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6118,7 +6338,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>43 SE Valle. Las 43 sedes del préstamo, todas de la Secretaría de Educación del Valle del Cauca. Es la línea base contra la que se mide cuánto cuesta ampliar el alcance. Sin volver a la base los fines de semana.</t>
+          <t>43 SE Valle. Las 43 sedes del préstamo, todas de la Secretaría de Educación del Valle del Cauca. Es la línea base contra la que se mide cuánto cuesta ampliar el alcance. Sin volver a la base los domingos.</t>
         </is>
       </c>
     </row>
@@ -6130,154 +6350,180 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Jornada</t>
+          <t>Semana de campo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hasta 8 horas contando carretera e inspecciones; cada inspección dura 3 horas.</t>
+          <t>De lunes a sábado, seis días. La semana 1 son los días 1 a 6, la 2 del 7 al 12, y así.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tiempos</t>
+          <t>Jornada</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mapbox, saliendo a las 7:00, entre sedes a las 11:00 y regresando a las 16:00 de un martes.</t>
+          <t>Hasta 8 horas contando carretera e inspecciones; cada inspección dura 3 horas.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Noches fuera</t>
+          <t>Tiempos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Una por cada día que la cuadrilla termina fuera de su base. Los fines de semana no se suman.</t>
+          <t>Mapbox, saliendo a las 7:00, entre sedes a las 11:00 y regresando a las 16:00 de un martes.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
+          <t>Noches fuera</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Una por cada día que la cuadrilla termina fuera de su base. El domingo de descanso no se suma acá; para el alojamiento que se paga están las noches de hotel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
           <t>Coordenadas</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Las marcadas en revisión son provisionales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Cuadrilla</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Días</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Sedes</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Horas de carretera</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Km</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Noches fuera</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>11</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" t="n">
-        <v>26</v>
-      </c>
-      <c r="E9" t="n">
-        <v>835</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5</v>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Cuadrilla</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Días</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Sedes</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Horas de carretera</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Km</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Noches fuera</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Noches de hotel</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>18.4</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>620</v>
+        <v>835</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>620</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B12" t="n">
         <v>11</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>16</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
         <v>23.1</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>817</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>10</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/public/datos/plan_cuadrillas_bid.xlsx
+++ b/public/datos/plan_cuadrillas_bid.xlsx
@@ -6350,7 +6350,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>

--- a/public/datos/plan_cuadrillas_bid.xlsx
+++ b/public/datos/plan_cuadrillas_bid.xlsx
@@ -6350,7 +6350,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
